--- a/output/pdf_financials_xlsx/HAWK.xlsx
+++ b/output/pdf_financials_xlsx/HAWK.xlsx
@@ -5899,46 +5899,46 @@
         <v>0.477479</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.478784</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.526454</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.528402</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.528402</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.553213</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.672951</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.670726</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.6985980000000001</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.768845</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.785628</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.857866</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.857866</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.857866</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.857866</v>
       </c>
     </row>
     <row r="93">
@@ -9877,7 +9877,11 @@
           <t>Reserves (notes 9 and 10)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -12603,7 +12607,11 @@
           <t>Reserves (note 9, note 10)</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -13159,7 +13167,11 @@
           <t>Reserves (note 10)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -14593,7 +14605,11 @@
           <t>Reserves (note 10) 526,454</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -15403,7 +15419,11 @@
           <t>Reserves (note 9 and 10)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HAWK.xlsx
+++ b/output/pdf_financials_xlsx/HAWK.xlsx
@@ -2414,13 +2414,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000822</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.001427</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0</v>
@@ -2432,16 +2432,16 @@
         <v>0</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.032877</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.002025</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.003774</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.005017</v>
       </c>
       <c r="R34" s="3" t="n">
         <v>0</v>
@@ -2530,13 +2530,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000822</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.001427</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0</v>
@@ -2548,16 +2548,16 @@
         <v>0</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.032877</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.002025</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.003774</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.005017</v>
       </c>
       <c r="R36" s="3" t="n">
         <v>0</v>
@@ -3226,13 +3226,13 @@
         <v>0.00185</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.002192</v>
+        <v>0.00137</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.0014</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.006677</v>
+        <v>0.00525</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.00175</v>
@@ -3244,16 +3244,16 @@
         <v>0.00175</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.034627</v>
+        <v>0.00175</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.210853</v>
+        <v>1.208828</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.005524</v>
+        <v>0.00175</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.010665</v>
+        <v>0.005648</v>
       </c>
       <c r="R48" s="3" t="n">
         <v>0.003237</v>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">

--- a/output/pdf_financials_xlsx/HAWK.xlsx
+++ b/output/pdf_financials_xlsx/HAWK.xlsx
@@ -2043,25 +2043,25 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.006343</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.004789</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.001816</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.003281</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.002589</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.001988</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.002097</v>
       </c>
       <c r="M28" s="3" t="n">
         <v>0.002418</v>
@@ -2101,25 +2101,25 @@
         <v>-1.215348</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.522033</v>
+        <v>-0.51569</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.301172</v>
+        <v>-0.296383</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.299037</v>
+        <v>-0.297221</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.335937</v>
+        <v>-0.332656</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.646878</v>
+        <v>-0.644289</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.309901</v>
+        <v>-0.307913</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.266505</v>
+        <v>-0.264408</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-0.255147</v>
@@ -6337,28 +6337,28 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.006343</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.004789</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.001816</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.003281</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.002589</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.001988</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.002097</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.002418</v>
       </c>
       <c r="N100" s="3" t="n">
         <v>0</v>
@@ -25271,7 +25271,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HAWK.xlsx
+++ b/output/pdf_financials_xlsx/HAWK.xlsx
@@ -6422,16 +6422,16 @@
         <v>0</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>-0.010097</v>
       </c>
       <c r="P101" s="3" t="n">
-        <v>0</v>
+        <v>-0.018095</v>
       </c>
       <c r="Q101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003146</v>
       </c>
       <c r="R101" s="3" t="n">
-        <v>0</v>
+        <v>-0.003111</v>
       </c>
     </row>
     <row r="102">
@@ -6718,10 +6718,10 @@
         <v>-0.626735</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.012537</v>
+        <v>0.009391</v>
       </c>
       <c r="R106" s="3" t="n">
-        <v>0.058141</v>
+        <v>0.05503</v>
       </c>
     </row>
     <row r="107">
@@ -6947,10 +6947,10 @@
         <v>0</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>0</v>
+        <v>0.006822</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>0.00588</v>
       </c>
       <c r="R110" s="3" t="n">
         <v>0</v>
@@ -6963,16 +6963,16 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005905</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.009898000000000001</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.014128</v>
       </c>
       <c r="F111" s="3" t="n">
         <v>0</v>
@@ -6984,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.00083</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -8351,16 +8351,16 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005905</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.009898000000000001</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.014128</v>
       </c>
       <c r="F134" s="3" t="n">
         <v>0</v>
@@ -8372,7 +8372,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.00083</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.112672</v>
+        <v>-0.118577</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.765869</v>
+        <v>-0.775767</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.345356</v>
+        <v>-0.359484</v>
       </c>
       <c r="F135" s="3" t="n">
         <v>0</v>
@@ -8434,7 +8434,7 @@
         <v>-0.231369</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.218605</v>
+        <v>-0.219435</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.439965</v>
@@ -17231,7 +17231,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>-</t>
@@ -18120,7 +18124,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>-</t>
@@ -19136,7 +19144,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -20049,7 +20061,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -22152,7 +22168,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -23972,7 +23992,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -26393,7 +26417,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -29335,7 +29363,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -30557,7 +30589,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -33333,7 +33369,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E252" s="5" t="n">
         <v>-0.005905</v>
       </c>
